--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.4.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.4.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -975,7 +975,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.4.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.4.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y129"/>
+  <dimension ref="A1:Y138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L16: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦â€¦</t>
+          <t>L33: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 :: CALAIS, ME. 一</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ " -</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L10: symbol-only separator/garbage line :: 215-11</t>
@@ -626,7 +630,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -642,7 +646,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L521: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: .for the very generous patronage you have given me since I opened up myâ€¢</t>
+          <t>L520: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • TO MY PATRONS-I wish to take this op- • nity of thanking you•</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -677,7 +681,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1211</t>
+          <t>781</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -700,12 +704,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN :: CALAIS, ME. ä¸€</t>
+          <t>L277: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: by Mr. Fielding ， the Liberal leader</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L33: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: goilâ€™s</t>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • " -</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -733,7 +737,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L524: line starts with punctuation glued to text :: .been a source of great -gement to me, but has permitted me toe</t>
+          <t>L521: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: .for the very generous patronage you have given me since I opened up my•</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -783,19 +787,19 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L176: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L537: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L64: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: countryâ€™s economic deliverance. By</t>
+          <t>L117: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: for a maternity branch • of Hosp tal</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L17: isolated marker/symbol line :: 368</t>
+          <t>L16: isolated marker/symbol line :: ……</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
@@ -816,7 +820,7 @@
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L1012: symbol-only separator/garbage line | line starts with punctuation glued to text :: * 600</t>
+          <t>L522: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Millinery Parlors in this city. The very sanguine way in which your sup- Y</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -834,12 +838,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>209</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>174</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -862,24 +866,24 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L363: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WANTEDâ€”A third class female teacher.</t>
+          <t>L705: stray/suspicious non-ASCII glyph(s): U+7528 CJK UNIFIED IDEOGRAPH-7528 | isolated marker/symbol line :: 用</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L98: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”Trustees Heard Suggestions at Monthly Meeting</t>
+          <t>L520: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • TO MY PATRONS-I wish to take this op- • nity of thanking you•</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L20: isolated marker/symbol line :: M</t>
+          <t>L17: isolated marker/symbol line :: 368</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L30: isolated marker/symbol line :: &gt;</t>
+          <t>L28: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • " -</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -889,11 +893,15 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L588: punctuation artifact: repeated periods :: Am. Copper........</t>
+          <t>L520: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • TO MY PATRONS-I wish to take this op- • nity of thanking you•</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L523: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • port has been given has surpassed my fullest expectations and has not only•</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -933,24 +941,24 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L401: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: MAPLE " â€œCREMOâ€�â€� FROST</t>
+          <t>L706: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Yesterdayâ€”New Annex to Cost About $12,000,</t>
+          <t>L521: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: .for the very generous patronage you have given me since I opened up my•</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 0.</t>
+          <t>L20: isolated marker/symbol line :: M</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L41: isolated marker/symbol line :: a</t>
+          <t>L30: isolated marker/symbol line :: &gt;</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr">
@@ -960,11 +968,15 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L590: punctuation artifact: repeated periods :: Am. Beet Sugar..</t>
+          <t>L588: punctuation artifact: repeated periods :: Am. Copper........</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
-      <c r="S6" s="1" t="inlineStr"/>
+      <c r="S6" s="1" t="inlineStr">
+        <is>
+          <t>L524: line starts with punctuation glued to text :: .been a source of great -gement to me, but has permitted me toe</t>
+        </is>
+      </c>
       <c r="T6" s="1" t="inlineStr"/>
       <c r="U6" s="1" t="inlineStr"/>
       <c r="V6" s="1" t="inlineStr"/>
@@ -1004,24 +1016,24 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L445: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: â€¦.</t>
+          <t>L707: stray/suspicious non-ASCII glyph(s): U+8D38 CJK UNIFIED IDEOGRAPH-8D38 | isolated marker/symbol line :: 贸</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L107: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: poâ€™nts about the best way to change</t>
+          <t>L522: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Millinery Parlors in this city. The very sanguine way in which your sup- Y</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 4</t>
+          <t>L39: isolated marker/symbol line :: 0.</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: 1</t>
+          <t>L41: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -1031,11 +1043,15 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L601: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
+          <t>L590: punctuation artifact: repeated periods :: Am. Beet Sugar..</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
-      <c r="S7" s="1" t="inlineStr"/>
+      <c r="S7" s="1" t="inlineStr">
+        <is>
+          <t>L525: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •select my stock for Fall from the leading British and American Millinery.</t>
+        </is>
+      </c>
       <c r="T7" s="1" t="inlineStr"/>
       <c r="U7" s="1" t="inlineStr"/>
       <c r="V7" s="1" t="inlineStr"/>
@@ -1075,24 +1091,24 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L501: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Gleaner office â€” 1 in</t>
+          <t>L719: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L117: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: for a maternity branch â€¢ of Hosp tal</t>
+          <t>L523: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • port has been given has surpassed my fullest expectations and has not only•</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L169: isolated marker/symbol line :: 4</t>
+          <t>L92: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 4</t>
+          <t>L43: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -1102,11 +1118,15 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L603: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 26%</t>
+          <t>L601: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
-      <c r="S8" s="1" t="inlineStr"/>
+      <c r="S8" s="1" t="inlineStr">
+        <is>
+          <t>L526: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •centerusting to be favored with a continuance of your esteemed patronage,.</t>
+        </is>
+      </c>
       <c r="T8" s="1" t="inlineStr"/>
       <c r="U8" s="1" t="inlineStr"/>
       <c r="V8" s="1" t="inlineStr"/>
@@ -1146,24 +1166,24 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L537: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L796: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: 95 at 30%，375 at 30.</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: enclosed $25 from St. Annâ€™s Church</t>
+          <t>L525: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •select my stock for Fall from the leading British and American Millinery.</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L170: isolated marker/symbol line :: 1</t>
+          <t>L169: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L55: isolated marker/symbol line :: -</t>
+          <t>L53: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr">
@@ -1173,11 +1193,15 @@
       </c>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>L605: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 4%</t>
+          <t>L603: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 26%</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr"/>
-      <c r="S9" s="1" t="inlineStr"/>
+      <c r="S9" s="1" t="inlineStr">
+        <is>
+          <t>L528: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Yours Very Respectfully,</t>
+        </is>
+      </c>
       <c r="T9" s="1" t="inlineStr"/>
       <c r="U9" s="1" t="inlineStr"/>
       <c r="V9" s="1" t="inlineStr"/>
@@ -1193,12 +1217,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1212,29 +1236,29 @@
       </c>
       <c r="I10" s="1" t="inlineStr">
         <is>
-          <t>L728: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 75c (letter/digit mix) :: Pricesâ€”75c, $1.00, $1.50.</t>
+          <t>L728: suspicious token(s): 75c (letter/digit mix) :: Prices—75c, $1.00, $1.50.</t>
         </is>
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L884: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L221: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ST. JOHNâ€”</t>
+          <t>L526: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •centerusting to be favored with a continuance of your esteemed patronage,.</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L171: isolated marker/symbol line :: 1</t>
+          <t>L170: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: )</t>
+          <t>L55: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr">
@@ -1244,11 +1268,15 @@
       </c>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>L607: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...42%</t>
+          <t>L605: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 4%</t>
         </is>
       </c>
       <c r="R10" s="1" t="inlineStr"/>
-      <c r="S10" s="1" t="inlineStr"/>
+      <c r="S10" s="1" t="inlineStr">
+        <is>
+          <t>L1012: symbol-only separator/garbage line | line starts with punctuation glued to text :: * 600</t>
+        </is>
+      </c>
       <c r="T10" s="1" t="inlineStr"/>
       <c r="U10" s="1" t="inlineStr"/>
       <c r="V10" s="1" t="inlineStr"/>
@@ -1269,7 +1297,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1288,24 +1316,24 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L896: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WOODSTOCKâ€”</t>
+          <t>L528: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Yours Very Respectfully,</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L172: isolated marker/symbol line :: m</t>
+          <t>L171: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: 2</t>
+          <t>L84: isolated marker/symbol line :: )</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr">
@@ -1315,11 +1343,15 @@
       </c>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L609: punctuation artifact: repeated periods :: Am. Cot. Oil......</t>
+          <t>L607: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...42%</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
-      <c r="S11" s="1" t="inlineStr"/>
+      <c r="S11" s="1" t="inlineStr">
+        <is>
+          <t>L1079: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •ing made in advertisements,•</t>
+        </is>
+      </c>
       <c r="T11" s="1" t="inlineStr"/>
       <c r="U11" s="1" t="inlineStr"/>
       <c r="V11" s="1" t="inlineStr"/>
@@ -1335,12 +1367,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>137</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1359,24 +1391,24 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L584: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): PATRoNS (odd internal casing) :: TO MY PATRoNS â€” I wish to take this Opr Â· nity of thanking you</t>
+          <t>L898: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L232: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Guy L. Hansonâ€™s Bookstore, Queen St.</t>
+          <t>L671: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L176: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | isolated marker/symbol line :: â€¦</t>
+          <t>L172: isolated marker/symbol line :: m</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L92: symbol-only separator/garbage line :: 1107</t>
+          <t>L90: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr">
@@ -1386,11 +1418,15 @@
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>L611: punctuation artifact: repeated periods :: Am. Loco..........</t>
+          <t>L609: punctuation artifact: repeated periods :: Am. Cot. Oil......</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr"/>
-      <c r="S12" s="1" t="inlineStr"/>
+      <c r="S12" s="1" t="inlineStr">
+        <is>
+          <t>L1083: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • publication.•</t>
+        </is>
+      </c>
       <c r="T12" s="1" t="inlineStr"/>
       <c r="U12" s="1" t="inlineStr"/>
       <c r="V12" s="1" t="inlineStr"/>
@@ -1411,7 +1447,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1420,7 +1456,7 @@
       <c r="G13" s="1" t="inlineStr"/>
       <c r="H13" s="1" t="inlineStr">
         <is>
-          <t>L584: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): PATRoNS (odd internal casing) :: TO MY PATRoNS â€” I wish to take this Opr Â· nity of thanking you</t>
+          <t>L584: suspicious token(s): PATRoNS (odd internal casing) :: TO MY PATRoNS — I wish to take this Opr · nity of thanking you</t>
         </is>
       </c>
       <c r="I13" s="1" t="inlineStr">
@@ -1430,24 +1466,24 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L705: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | isolated marker/symbol line :: ç”¨</t>
+          <t>L943: stray/suspicious non-ASCII glyph(s): U+6E90 CJK UNIFIED IDEOGRAPH-6E90 | isolated marker/symbol line :: 源</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: OTTAWAâ€”</t>
+          <t>L1078: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: ♦ in order to ensure changes be-•</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L180: symbol-only separator/garbage line :: , 000.</t>
+          <t>L176: isolated marker/symbol line :: …</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: A</t>
+          <t>L92: symbol-only separator/garbage line :: 1107</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr">
@@ -1457,7 +1493,7 @@
       </c>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>L613: punctuation artifact: repeated periods :: Am. Sm. and Ref..</t>
+          <t>L611: punctuation artifact: repeated periods :: Am. Loco..........</t>
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr"/>
@@ -1482,7 +1518,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1496,29 +1532,25 @@
       </c>
       <c r="I14" s="1" t="inlineStr">
         <is>
-          <t>L1068: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 4a (letter/digit mix) :: â€”4a t 215; Nova Scotiaâ€”1.1 at 251;</t>
-        </is>
-      </c>
-      <c r="J14" s="1" t="inlineStr">
-        <is>
-          <t>L706: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
+          <t>L1068: suspicious token(s): 4a (letter/digit mix) :: —4a t 215; Nova Scotia—1.1 at 251;</t>
+        </is>
+      </c>
+      <c r="J14" s="1" t="inlineStr"/>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L252: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: BANGOR, ME.â€”</t>
+          <t>L1079: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •ing made in advertisements,•</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L200: isolated marker/symbol line :: A</t>
+          <t>L180: symbol-only separator/garbage line :: , 000.</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: *</t>
+          <t>L96: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr">
@@ -1528,7 +1560,7 @@
       </c>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>L617: punctuation artifact: repeated periods :: Am. Sugar..........</t>
+          <t>L613: punctuation artifact: repeated periods :: Am. Sm. and Ref..</t>
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
@@ -1570,26 +1602,22 @@
           <t>L1089: suspicious token(s): Fi38 (letter/digit mix) :: MEATS AND Fi38</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
-        <is>
-          <t>L707: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00B8 CEDILLA | isolated marker/symbol line :: è´¸</t>
-        </is>
-      </c>
+      <c r="J15" s="1" t="inlineStr"/>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L257: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: HOULTON, ME.â€”</t>
+          <t>L1080: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ copy must reach this office not •</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L236: isolated marker/symbol line :: 1</t>
+          <t>L200: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: %</t>
+          <t>L101: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr">
@@ -1599,7 +1627,7 @@
       </c>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>L619: punctuation artifact: repeated periods :: An. Copper........</t>
+          <t>L617: punctuation artifact: repeated periods :: Am. Sugar..........</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
@@ -1637,26 +1665,22 @@
         </is>
       </c>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L719: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L269: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: say that hâ€™s Government would not</t>
+          <t>L1081: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: later than 9 a. m. on the day of •</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L238: isolated marker/symbol line :: 1</t>
+          <t>L236: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L223: isolated marker/symbol line :: L.</t>
+          <t>L103: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr">
@@ -1666,7 +1690,7 @@
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>L621: punctuation artifact: repeated periods :: Atchison...........</t>
+          <t>L619: punctuation artifact: repeated periods :: An. Copper........</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
@@ -1704,26 +1728,22 @@
         </is>
       </c>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L743: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â€¦... 20%</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L337: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ladiesâ€™ committee have now $1,000.</t>
+          <t>L1083: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • publication.•</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L291: isolated marker/symbol line :: :</t>
+          <t>L238: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L355: isolated marker/symbol line :: !/</t>
+          <t>L223: isolated marker/symbol line :: L.</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr">
@@ -1733,7 +1753,7 @@
       </c>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>L623: punctuation artifact: repeated periods :: Balt, and Ohio....</t>
+          <t>L621: punctuation artifact: repeated periods :: Atchison...........</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr"/>
@@ -1759,26 +1779,22 @@
         </is>
       </c>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L781: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Crown â€” 2, 070 at 275, 100 at 279, 25</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€ž</t>
+          <t>L1125: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: some interesting stereoptic view•</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L298: isolated marker/symbol line :: 1</t>
+          <t>L291: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L364: isolated marker/symbol line :: 66</t>
+          <t>L355: isolated marker/symbol line :: !/</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr">
@@ -1788,7 +1804,7 @@
       </c>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>L624: punctuation artifact: repeated periods :: B. R. T............</t>
+          <t>L623: punctuation artifact: repeated periods :: Balt, and Ohio....</t>
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr"/>
@@ -1814,26 +1830,18 @@
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L884: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L373: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: at 3.30 oâ€™clock. All members are request-</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L339: isolated marker/symbol line :: 7</t>
+          <t>L298: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L458: symbol-only separator/garbage line :: 613.</t>
+          <t>L357: isolated marker/symbol line :: 1°</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr">
@@ -1843,7 +1851,7 @@
       </c>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>L626: punctuation artifact: repeated periods :: C. P. R............</t>
+          <t>L624: punctuation artifact: repeated periods :: B. R. T............</t>
         </is>
       </c>
       <c r="R19" s="1" t="inlineStr"/>
@@ -1865,26 +1873,18 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L896: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L407: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: New York, Aug. 5.â€”The opening</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L373: symbol-only separator/garbage line :: 613.</t>
+          <t>L339: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L480: isolated marker/symbol line :: .</t>
+          <t>L364: isolated marker/symbol line :: 66</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>L628: punctuation artifact: repeated periods :: Chesa. and Ohio..</t>
+          <t>L626: punctuation artifact: repeated periods :: C. P. R............</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
@@ -1916,26 +1916,18 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L897: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: - DEALER IN â€”</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L423: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ton, Secâ€™y to Trustees, McGivney June-</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L374: isolated marker/symbol line :: e</t>
+          <t>L373: symbol-only separator/garbage line :: 613.</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L516: isolated marker/symbol line :: 6</t>
+          <t>L369: isolated marker/symbol line :: „</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr">
@@ -1945,7 +1937,7 @@
       </c>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>L631: punctuation artifact: repeated periods :: Col Fuel and Iron..</t>
+          <t>L628: punctuation artifact: repeated periods :: Chesa. and Ohio..</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr"/>
@@ -1967,26 +1959,18 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L898: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L424: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: tion, N. B.â€”641 d</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L403: isolated marker/symbol line :: 1</t>
+          <t>L374: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L518: symbol-only separator/garbage line :: ;*******************************</t>
+          <t>L458: symbol-only separator/garbage line :: 613.</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr">
@@ -1996,7 +1980,7 @@
       </c>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L633: punctuation artifact: repeated periods :: Chino Copper..</t>
+          <t>L631: punctuation artifact: repeated periods :: Col Fuel and Iron..</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
@@ -2018,26 +2002,18 @@
       <c r="G23" s="1" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L943: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: æº�</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L450: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: duced a good effect on sentiment. U. â€”â€”</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L404: isolated marker/symbol line :: 2</t>
+          <t>L403: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L532: symbol-only separator/garbage line :: *******************</t>
+          <t>L480: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr">
@@ -2047,7 +2023,7 @@
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
-          <t>L635: punctuation artifact: repeated periods :: Con. Gas.........</t>
+          <t>L633: punctuation artifact: repeated periods :: Chino Copper..</t>
         </is>
       </c>
       <c r="R23" s="1" t="inlineStr"/>
@@ -2070,21 +2046,17 @@
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L451: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: LOSTâ€”Gentâ€™s gold watch fob.</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L405: isolated marker/symbol line :: T</t>
+          <t>L404: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L545: isolated marker/symbol line :: 71</t>
+          <t>L516: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr">
@@ -2094,7 +2066,7 @@
       </c>
       <c r="Q24" s="1" t="inlineStr">
         <is>
-          <t>L637: punctuation artifact: repeated periods :: Erie..............</t>
+          <t>L635: punctuation artifact: repeated periods :: Con. Gas.........</t>
         </is>
       </c>
       <c r="R24" s="1" t="inlineStr"/>
@@ -2117,21 +2089,17 @@
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L457: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 will kindly leave at Gleaner officeâ€”1 in</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L410: isolated marker/symbol line :: 71</t>
+          <t>L405: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L546: symbol-only separator/garbage line :: 27%</t>
+          <t>L518: symbol-only separator/garbage line :: ;*******************************</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr">
@@ -2141,7 +2109,7 @@
       </c>
       <c r="Q25" s="1" t="inlineStr">
         <is>
-          <t>L639: punctuation artifact: repeated periods :: Erie, 1st Pfd.....</t>
+          <t>L637: punctuation artifact: repeated periods :: Erie..............</t>
         </is>
       </c>
       <c r="R25" s="1" t="inlineStr"/>
@@ -2164,21 +2132,17 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L505: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: requested to flâ€™e the same, duly attested,</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L412: symbol-only separator/garbage line :: 27%</t>
+          <t>L410: isolated marker/symbol line :: 71</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L548: isolated marker/symbol line :: 45</t>
+          <t>L532: symbol-only separator/garbage line :: *******************</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr">
@@ -2188,7 +2152,7 @@
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
-          <t>L641: punctuation artifact: repeated periods :: Gen. Elec..........</t>
+          <t>L639: punctuation artifact: repeated periods :: Erie, 1st Pfd.....</t>
         </is>
       </c>
       <c r="R26" s="1" t="inlineStr"/>
@@ -2211,21 +2175,17 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L520: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ TO MY PATRONS-I wish to take this op- â€¢ nity of thanking youâ€¢</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L414: isolated marker/symbol line :: 45</t>
+          <t>L412: symbol-only separator/garbage line :: 27%</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L550: symbol-only separator/garbage line :: 43%</t>
+          <t>L545: isolated marker/symbol line :: 71</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr">
@@ -2235,7 +2195,7 @@
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L643: punctuation artifact: repeated periods :: Gr. Nor. Pfd.......</t>
+          <t>L641: punctuation artifact: repeated periods :: Gen. Elec..........</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2258,21 +2218,17 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L521: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | line starts with punctuation glued to text :: .for the very generous patronage you have given me since I opened up myâ€¢</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L416: symbol-only separator/garbage line :: 43%</t>
+          <t>L414: isolated marker/symbol line :: 45</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L552: symbol-only separator/garbage line :: 3132</t>
+          <t>L546: symbol-only separator/garbage line :: 27%</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr">
@@ -2282,7 +2238,7 @@
       </c>
       <c r="Q28" s="1" t="inlineStr">
         <is>
-          <t>L645: punctuation artifact: repeated periods :: Gr. Nor. Ore........</t>
+          <t>L643: punctuation artifact: repeated periods :: Gr. Nor. Pfd.......</t>
         </is>
       </c>
       <c r="R28" s="1" t="inlineStr"/>
@@ -2305,21 +2261,17 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L522: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Millinery Parlors in this city. The very sanguine way in which your sup- Y</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L418: isolated marker/symbol line :: .</t>
+          <t>L416: symbol-only separator/garbage line :: 43%</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L554: symbol-only separator/garbage line :: 63%</t>
+          <t>L548: isolated marker/symbol line :: 45</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr">
@@ -2329,7 +2281,7 @@
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
-          <t>L647: punctuation artifact: repeated periods :: ill. Cent............</t>
+          <t>L645: punctuation artifact: repeated periods :: Gr. Nor. Ore........</t>
         </is>
       </c>
       <c r="R29" s="1" t="inlineStr"/>
@@ -2352,21 +2304,17 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L523: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ port has been given has surpassed my fullest expectations and has not onlyâ€¢</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L419: symbol-only separator/garbage line :: 31%</t>
+          <t>L418: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L556: symbol-only separator/garbage line :: 128%</t>
+          <t>L550: symbol-only separator/garbage line :: 43%</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr">
@@ -2376,7 +2324,7 @@
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
-          <t>L649: punctuation artifact: repeated periods :: Int. Met............</t>
+          <t>L647: punctuation artifact: repeated periods :: ill. Cent............</t>
         </is>
       </c>
       <c r="R30" s="1" t="inlineStr"/>
@@ -2399,21 +2347,17 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L525: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢select my stock for Fall from the leading British and American Millinery.</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L421: symbol-only separator/garbage line :: 63.%</t>
+          <t>L419: symbol-only separator/garbage line :: 31%</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L558: symbol-only separator/garbage line :: 110%</t>
+          <t>L552: symbol-only separator/garbage line :: 3132</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr">
@@ -2423,7 +2367,7 @@
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
-          <t>L651: punctuation artifact: repeated periods :: Louis, and Nash...</t>
+          <t>L649: punctuation artifact: repeated periods :: Int. Met............</t>
         </is>
       </c>
       <c r="R31" s="1" t="inlineStr"/>
@@ -2446,21 +2390,17 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L526: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢centerusting to be favored with a continuance of your esteemed patronage,.</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L423: symbol-only separator/garbage line :: 128%</t>
+          <t>L421: symbol-only separator/garbage line :: 63.%</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L560: isolated marker/symbol line :: 36</t>
+          <t>L554: symbol-only separator/garbage line :: 63%</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr">
@@ -2470,7 +2410,7 @@
       </c>
       <c r="Q32" s="1" t="inlineStr">
         <is>
-          <t>L653: punctuation artifact: repeated periods :: Lehigh Valley.......</t>
+          <t>L651: punctuation artifact: repeated periods :: Louis, and Nash...</t>
         </is>
       </c>
       <c r="R32" s="1" t="inlineStr"/>
@@ -2493,21 +2433,17 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L528: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Yours Very Respectfully,</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L425: isolated marker/symbol line :: .</t>
+          <t>L423: symbol-only separator/garbage line :: 128%</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L562: symbol-only separator/garbage line :: 97%</t>
+          <t>L556: symbol-only separator/garbage line :: 128%</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr">
@@ -2517,7 +2453,7 @@
       </c>
       <c r="Q33" s="1" t="inlineStr">
         <is>
-          <t>L655: punctuation artifact: repeated periods :: Kansas City So., ..</t>
+          <t>L653: punctuation artifact: repeated periods :: Lehigh Valley.......</t>
         </is>
       </c>
       <c r="R33" s="1" t="inlineStr"/>
@@ -2540,21 +2476,17 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L577: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: 29% PEAK FREAN &amp; COâ€™S</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L426: isolated marker/symbol line :: .</t>
+          <t>L425: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L564: symbol-only separator/garbage line :: 96%</t>
+          <t>L558: symbol-only separator/garbage line :: 110%</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr">
@@ -2564,7 +2496,7 @@
       </c>
       <c r="Q34" s="1" t="inlineStr">
         <is>
-          <t>L657: punctuation artifact: repeated periods :: Miss., Kan. and Tex.. .. 22%</t>
+          <t>L655: punctuation artifact: repeated periods :: Kansas City So., ..</t>
         </is>
       </c>
       <c r="R34" s="1" t="inlineStr"/>
@@ -2587,21 +2519,17 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L671: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L429: symbol-only separator/garbage line :: . 36</t>
+          <t>L426: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L565: isolated marker/symbol line :: 8</t>
+          <t>L560: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr">
@@ -2611,7 +2539,7 @@
       </c>
       <c r="Q35" s="1" t="inlineStr">
         <is>
-          <t>L719: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 88</t>
+          <t>L657: punctuation artifact: repeated periods :: Miss., Kan. and Tex.. .. 22%</t>
         </is>
       </c>
       <c r="R35" s="1" t="inlineStr"/>
@@ -2634,21 +2562,17 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L728: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 75c (letter/digit mix) :: Pricesâ€”75c, $1.00, $1.50.</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L430: isolated marker/symbol line :: 36</t>
+          <t>L427: symbol-only separator/garbage line :: 110 ½</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L567: symbol-only separator/garbage line :: 215%</t>
+          <t>L562: symbol-only separator/garbage line :: 97%</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr">
@@ -2658,7 +2582,7 @@
       </c>
       <c r="Q36" s="1" t="inlineStr">
         <is>
-          <t>L756: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 31%</t>
+          <t>L719: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 88</t>
         </is>
       </c>
       <c r="R36" s="1" t="inlineStr"/>
@@ -2681,21 +2605,17 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L833: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: 1905 to 1911 with much satisfaction. Peopleâ€™s Gas...............................................</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L432: symbol-only separator/garbage line :: . 96%</t>
+          <t>L429: symbol-only separator/garbage line :: . 36</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L568: symbol-only separator/garbage line :: 55%</t>
+          <t>L564: symbol-only separator/garbage line :: 96%</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr">
@@ -2705,7 +2625,7 @@
       </c>
       <c r="Q37" s="1" t="inlineStr">
         <is>
-          <t>L758: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 39%</t>
+          <t>L756: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 31%</t>
         </is>
       </c>
       <c r="R37" s="1" t="inlineStr"/>
@@ -2728,31 +2648,27 @@
       <c r="H38" s="1" t="inlineStr"/>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L841: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: of the Board of Health officially in-â€œSooâ€�</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L433: isolated marker/symbol line :: 97</t>
+          <t>L430: isolated marker/symbol line :: 36</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L570: symbol-only separator/garbage line :: 106%</t>
+          <t>L565: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr">
         <is>
-          <t>L743: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR | punctuation artifact: repeated periods :: â€¦... 20%</t>
+          <t>L743: symbol-only separator/garbage line | punctuation artifact: repeated periods :: …... 20%</t>
         </is>
       </c>
       <c r="Q38" s="1" t="inlineStr">
         <is>
-          <t>L760: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...131%</t>
+          <t>L758: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 39%</t>
         </is>
       </c>
       <c r="R38" s="1" t="inlineStr"/>
@@ -2775,21 +2691,17 @@
       <c r="H39" s="1" t="inlineStr"/>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L899: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: the distance. â€œEvery reduction made</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L435: symbol-only separator/garbage line :: 9614</t>
+          <t>L432: symbol-only separator/garbage line :: . 96%</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L572: symbol-only separator/garbage line :: 31%</t>
+          <t>L567: symbol-only separator/garbage line :: 215%</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr">
@@ -2799,7 +2711,7 @@
       </c>
       <c r="Q39" s="1" t="inlineStr">
         <is>
-          <t>L762: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...29%</t>
+          <t>L760: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...131%</t>
         </is>
       </c>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2822,21 +2734,17 @@
       <c r="H40" s="1" t="inlineStr"/>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L985: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Car Fdyâ€”15 at 67.</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L437: symbol-only separator/garbage line :: . 88</t>
+          <t>L433: isolated marker/symbol line :: 97</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr">
         <is>
-          <t>L574: symbol-only separator/garbage line :: 39%</t>
+          <t>L568: symbol-only separator/garbage line :: 55%</t>
         </is>
       </c>
       <c r="P40" s="1" t="inlineStr">
@@ -2846,7 +2754,7 @@
       </c>
       <c r="Q40" s="1" t="inlineStr">
         <is>
-          <t>L774: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...15% - - |</t>
+          <t>L762: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...29%</t>
         </is>
       </c>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2869,21 +2777,17 @@
       <c r="H41" s="1" t="inlineStr"/>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L993: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Cement Pfd.â€”2 at 89%. 31 at 90.</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L438: isolated marker/symbol line :: 8</t>
+          <t>L435: symbol-only separator/garbage line :: 9614</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>L575: symbol-only separator/garbage line :: 131%</t>
+          <t>L570: symbol-only separator/garbage line :: 106%</t>
         </is>
       </c>
       <c r="P41" s="1" t="inlineStr">
@@ -2893,7 +2797,7 @@
       </c>
       <c r="Q41" s="1" t="inlineStr">
         <is>
-          <t>L776: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...134% 134%</t>
+          <t>L774: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...15% - - |</t>
         </is>
       </c>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2916,21 +2820,17 @@
       <c r="H42" s="1" t="inlineStr"/>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L995: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: C. P. R.â€”25 at 216%, 100 at 216%.</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L440: symbol-only separator/garbage line :: 215%</t>
+          <t>L437: symbol-only separator/garbage line :: . 88</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr">
         <is>
-          <t>L579: symbol-only separator/garbage line :: 46%</t>
+          <t>L572: symbol-only separator/garbage line :: 31%</t>
         </is>
       </c>
       <c r="P42" s="1" t="inlineStr">
@@ -2940,7 +2840,7 @@
       </c>
       <c r="Q42" s="1" t="inlineStr">
         <is>
-          <t>L778: symbol-only separator/garbage line | punctuation artifact: repeated periods :: , ..150% 151%</t>
+          <t>L776: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...134% 134%</t>
         </is>
       </c>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2963,21 +2863,17 @@
       <c r="H43" s="1" t="inlineStr"/>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L1039: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Dom Ironâ€”160 at 44.</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L442: symbol-only separator/garbage line :: . 55</t>
+          <t>L438: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr">
         <is>
-          <t>L580: symbol-only separator/garbage line :: 140%</t>
+          <t>L574: symbol-only separator/garbage line :: 39%</t>
         </is>
       </c>
       <c r="P43" s="1" t="inlineStr">
@@ -2987,7 +2883,7 @@
       </c>
       <c r="Q43" s="1" t="inlineStr">
         <is>
-          <t>L831: punctuation artifact: repeated periods :: Miss Katherine Haggarty (Sister Pac. Mail.......................................................</t>
+          <t>L778: symbol-only separator/garbage line | punctuation artifact: repeated periods :: , ..150% 151%</t>
         </is>
       </c>
       <c r="R43" s="1" t="inlineStr"/>
@@ -3010,21 +2906,17 @@
       <c r="H44" s="1" t="inlineStr"/>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L1041: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Iron Pfd.â€”15 at 93%. 10 at 93%.</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L446: symbol-only separator/garbage line :: 106%</t>
+          <t>L440: symbol-only separator/garbage line :: 215%</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>L582: symbol-only separator/garbage line :: 126%</t>
+          <t>L575: symbol-only separator/garbage line :: 131%</t>
         </is>
       </c>
       <c r="P44" s="1" t="inlineStr">
@@ -3034,7 +2926,7 @@
       </c>
       <c r="Q44" s="1" t="inlineStr">
         <is>
-          <t>L832: punctuation artifact: repeated periods :: Clarice), who filled the position from penn ex div..............................................</t>
+          <t>L831: punctuation artifact: repeated periods :: Miss Katherine Haggarty (Sister Pac. Mail.......................................................</t>
         </is>
       </c>
       <c r="R44" s="1" t="inlineStr"/>
@@ -3057,21 +2949,17 @@
       <c r="H45" s="1" t="inlineStr"/>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L1043: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Brazilâ€”35 at 85%.</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L448: symbol-only separator/garbage line :: . 31%</t>
+          <t>L442: symbol-only separator/garbage line :: . 55</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr">
         <is>
-          <t>L584: symbol-only separator/garbage line :: 35%</t>
+          <t>L579: symbol-only separator/garbage line :: 46%</t>
         </is>
       </c>
       <c r="P45" s="1" t="inlineStr">
@@ -3081,7 +2969,7 @@
       </c>
       <c r="Q45" s="1" t="inlineStr">
         <is>
-          <t>L833: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: repeated periods :: 1905 to 1911 with much satisfaction. Peopleâ€™s Gas...............................................</t>
+          <t>L832: punctuation artifact: repeated periods :: Clarice), who filled the position from penn ex div..............................................</t>
         </is>
       </c>
       <c r="R45" s="1" t="inlineStr"/>
@@ -3104,21 +2992,17 @@
       <c r="H46" s="1" t="inlineStr"/>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L1045: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Bridgeâ€”25 at 116.</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L449: symbol-only separator/garbage line :: 31%</t>
+          <t>L443: symbol-only separator/garbage line :: 55 ½</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr">
         <is>
-          <t>L586: isolated marker/symbol line :: 107</t>
+          <t>L580: symbol-only separator/garbage line :: 140%</t>
         </is>
       </c>
       <c r="P46" s="1" t="inlineStr">
@@ -3128,7 +3012,7 @@
       </c>
       <c r="Q46" s="1" t="inlineStr">
         <is>
-          <t>L840: punctuation artifact: repeated periods :: evening meeting from the Secretary So Pacific...</t>
+          <t>L833: punctuation artifact: repeated periods :: 1905 to 1911 with much satisfaction. People’s Gas...............................................</t>
         </is>
       </c>
       <c r="R46" s="1" t="inlineStr"/>
@@ -3151,21 +3035,17 @@
       <c r="H47" s="1" t="inlineStr"/>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L1047: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Scotiaâ€”25 at 73.</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L451: isolated marker/symbol line :: 00</t>
+          <t>L445: isolated marker/symbol line :: ….</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>L601: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
+          <t>L582: symbol-only separator/garbage line :: 126%</t>
         </is>
       </c>
       <c r="P47" s="1" t="inlineStr">
@@ -3175,7 +3055,7 @@
       </c>
       <c r="Q47" s="1" t="inlineStr">
         <is>
-          <t>L842: punctuation artifact: repeated periods :: Sou. Ry...................................................</t>
+          <t>L840: punctuation artifact: repeated periods :: evening meeting from the Secretary So Pacific...</t>
         </is>
       </c>
       <c r="R47" s="1" t="inlineStr"/>
@@ -3198,21 +3078,17 @@
       <c r="H48" s="1" t="inlineStr"/>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L1049: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Quebecâ€”20 at 12.</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L452: symbol-only separator/garbage line :: . 39%</t>
+          <t>L446: symbol-only separator/garbage line :: 106%</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr">
         <is>
-          <t>L603: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 26%</t>
+          <t>L584: symbol-only separator/garbage line :: 35%</t>
         </is>
       </c>
       <c r="P48" s="1" t="inlineStr">
@@ -3222,7 +3098,7 @@
       </c>
       <c r="Q48" s="1" t="inlineStr">
         <is>
-          <t>L843: punctuation artifact: repeated periods :: Utah Copper..</t>
+          <t>L842: punctuation artifact: repeated periods :: Sou. Ry...................................................</t>
         </is>
       </c>
       <c r="R48" s="1" t="inlineStr"/>
@@ -3245,21 +3121,17 @@
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L1051: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Span. Riverâ€”85 at 30, 250 at 40%,</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L453: symbol-only separator/garbage line :: 39%</t>
+          <t>L448: symbol-only separator/garbage line :: . 31%</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr">
         <is>
-          <t>L605: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 4%</t>
+          <t>L586: isolated marker/symbol line :: 107</t>
         </is>
       </c>
       <c r="P49" s="1" t="inlineStr">
@@ -3269,7 +3141,7 @@
       </c>
       <c r="Q49" s="1" t="inlineStr">
         <is>
-          <t>L844: punctuation artifact: repeated periods :: Un. Pacific...</t>
+          <t>L843: punctuation artifact: repeated periods :: Utah Copper..</t>
         </is>
       </c>
       <c r="R49" s="1" t="inlineStr"/>
@@ -3292,21 +3164,17 @@
       <c r="H50" s="1" t="inlineStr"/>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L1054: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Toronto Râ€™yâ€”25 at 138%2, 1 at 139.</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L455: symbol-only separator/garbage line :: 131%</t>
+          <t>L449: symbol-only separator/garbage line :: 31%</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>L607: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...42%</t>
+          <t>L601: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 71</t>
         </is>
       </c>
       <c r="P50" s="1" t="inlineStr">
@@ -3316,7 +3184,7 @@
       </c>
       <c r="Q50" s="1" t="inlineStr">
         <is>
-          <t>L846: punctuation artifact: repeated periods :: U. S. Steel..</t>
+          <t>L844: punctuation artifact: repeated periods :: Un. Pacific...</t>
         </is>
       </c>
       <c r="R50" s="1" t="inlineStr"/>
@@ -3339,27 +3207,23 @@
       <c r="H51" s="1" t="inlineStr"/>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L1056: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ogilvieâ€”85 at 112.</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L456: symbol-only separator/garbage line :: 131%</t>
+          <t>L451: isolated marker/symbol line :: 00</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr">
         <is>
-          <t>L667: symbol-only separator/garbage line :: 20%</t>
+          <t>L603: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 26%</t>
         </is>
       </c>
       <c r="P51" s="1" t="inlineStr"/>
       <c r="Q51" s="1" t="inlineStr">
         <is>
-          <t>L859: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..113% 112%</t>
+          <t>L846: punctuation artifact: repeated periods :: U. S. Steel..</t>
         </is>
       </c>
       <c r="R51" s="1" t="inlineStr"/>
@@ -3382,27 +3246,23 @@
       <c r="H52" s="1" t="inlineStr"/>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L1058: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tuckettsâ€”5 at 40%.</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L458: symbol-only separator/garbage line :: . 29%</t>
+          <t>L452: symbol-only separator/garbage line :: . 39%</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr">
         <is>
-          <t>L669: symbol-only separator/garbage line :: 61%</t>
+          <t>L605: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 4%</t>
         </is>
       </c>
       <c r="P52" s="1" t="inlineStr"/>
       <c r="Q52" s="1" t="inlineStr">
         <is>
-          <t>L861: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..114% 114%</t>
+          <t>L859: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..113% 112%</t>
         </is>
       </c>
       <c r="R52" s="1" t="inlineStr"/>
@@ -3425,27 +3285,23 @@
       <c r="H53" s="1" t="inlineStr"/>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L1060: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawaâ€”13 at 151.</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L459: symbol-only separator/garbage line :: 29%</t>
+          <t>L453: symbol-only separator/garbage line :: 39%</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>L671: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L607: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...42%</t>
         </is>
       </c>
       <c r="P53" s="1" t="inlineStr"/>
       <c r="Q53" s="1" t="inlineStr">
         <is>
-          <t>L863: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..159% 159%</t>
+          <t>L861: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..114% 114%</t>
         </is>
       </c>
       <c r="R53" s="1" t="inlineStr"/>
@@ -3468,27 +3324,23 @@
       <c r="H54" s="1" t="inlineStr"/>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L1062: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tex. Pfd.â€”1 at 99, 1 at 99%. 2 at</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L461: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L455: symbol-only separator/garbage line :: 131%</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr">
         <is>
-          <t>L673: symbol-only separator/garbage line :: *********</t>
+          <t>L667: symbol-only separator/garbage line :: 20%</t>
         </is>
       </c>
       <c r="P54" s="1" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr">
         <is>
-          <t>L919: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ......126% 127%</t>
+          <t>L863: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..159% 159%</t>
         </is>
       </c>
       <c r="R54" s="1" t="inlineStr"/>
@@ -3511,27 +3363,23 @@
       <c r="H55" s="1" t="inlineStr"/>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L1065: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Bondsâ€”Coalâ€”1000 at 97.</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L462: symbol-only separator/garbage line :: 46%</t>
+          <t>L456: symbol-only separator/garbage line :: 131%</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr">
         <is>
-          <t>L713: symbol-only separator/garbage line :: .36</t>
+          <t>L669: symbol-only separator/garbage line :: 61%</t>
         </is>
       </c>
       <c r="P55" s="1" t="inlineStr"/>
       <c r="Q55" s="1" t="inlineStr">
         <is>
-          <t>L921: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 24% 24%</t>
+          <t>L919: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ......126% 127%</t>
         </is>
       </c>
       <c r="R55" s="1" t="inlineStr"/>
@@ -3554,27 +3402,23 @@
       <c r="H56" s="1" t="inlineStr"/>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L1067: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Banksâ€”Commerceâ€”4 at 200; Royal</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L464: isolated marker/symbol line :: .</t>
+          <t>L458: symbol-only separator/garbage line :: . 29%</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>L715: symbol-only separator/garbage line :: .96%</t>
+          <t>L671: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P56" s="1" t="inlineStr"/>
       <c r="Q56" s="1" t="inlineStr">
         <is>
-          <t>L923: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 49% 49%</t>
+          <t>L921: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 24% 24%</t>
         </is>
       </c>
       <c r="R56" s="1" t="inlineStr"/>
@@ -3597,27 +3441,23 @@
       <c r="H57" s="1" t="inlineStr"/>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L1068: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): 4a (letter/digit mix) :: â€”4a t 215; Nova Scotiaâ€”1.1 at 251;</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L465: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
+          <t>L459: symbol-only separator/garbage line :: 29%</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr">
         <is>
-          <t>L717: symbol-only separator/garbage line :: .96</t>
+          <t>L673: symbol-only separator/garbage line :: *********</t>
         </is>
       </c>
       <c r="P57" s="1" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr">
         <is>
-          <t>L925: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...149% 150%</t>
+          <t>L923: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 49% 49%</t>
         </is>
       </c>
       <c r="R57" s="1" t="inlineStr"/>
@@ -3640,27 +3480,23 @@
       <c r="H58" s="1" t="inlineStr"/>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L1069: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Montreal-4 at 228; Molson;â€”5 at</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L466: symbol-only separator/garbage line :: 140%</t>
+          <t>L461: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr">
         <is>
-          <t>L719: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 88</t>
+          <t>L713: symbol-only separator/garbage line :: .36</t>
         </is>
       </c>
       <c r="P58" s="1" t="inlineStr"/>
       <c r="Q58" s="1" t="inlineStr">
         <is>
-          <t>L976: punctuation artifact: repeated periods :: Virginia Chem.........25%</t>
+          <t>L925: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...149% 150%</t>
         </is>
       </c>
       <c r="R58" s="1" t="inlineStr"/>
@@ -3683,27 +3519,23 @@
       <c r="H59" s="1" t="inlineStr"/>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L1078: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ in order to ensure changes be-â€¢</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L468: symbol-only separator/garbage line :: . 125%</t>
+          <t>L462: symbol-only separator/garbage line :: 46%</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>L721: symbol-only separator/garbage line :: .217%</t>
+          <t>L715: symbol-only separator/garbage line :: .96%</t>
         </is>
       </c>
       <c r="P59" s="1" t="inlineStr"/>
       <c r="Q59" s="1" t="inlineStr">
         <is>
-          <t>L978: punctuation artifact: repeated periods :: Western Union...........</t>
+          <t>L976: punctuation artifact: repeated periods :: Virginia Chem.........25%</t>
         </is>
       </c>
       <c r="R59" s="1" t="inlineStr"/>
@@ -3726,25 +3558,25 @@
       <c r="H60" s="1" t="inlineStr"/>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L1079: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ing made in advertisements,â€¢</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L469: symbol-only separator/garbage line :: 126%</t>
+          <t>L464: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr">
         <is>
-          <t>L723: symbol-only separator/garbage line :: .55</t>
+          <t>L717: symbol-only separator/garbage line :: .96</t>
         </is>
       </c>
       <c r="P60" s="1" t="inlineStr"/>
-      <c r="Q60" s="1" t="inlineStr"/>
+      <c r="Q60" s="1" t="inlineStr">
+        <is>
+          <t>L978: punctuation artifact: repeated periods :: Western Union...........</t>
+        </is>
+      </c>
       <c r="R60" s="1" t="inlineStr"/>
       <c r="S60" s="1" t="inlineStr"/>
       <c r="T60" s="1" t="inlineStr"/>
@@ -3765,25 +3597,25 @@
       <c r="H61" s="1" t="inlineStr"/>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1080: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ copy must reach this office not â€¢</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L471: symbol-only separator/garbage line :: 35%</t>
+          <t>L465: isolated marker/symbol line | punctuation artifact: repeated periods :: ...</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr">
         <is>
-          <t>L756: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 31%</t>
+          <t>L719: symbol-only separator/garbage line | punctuation artifact: repeated periods :: .. 88</t>
         </is>
       </c>
       <c r="P61" s="1" t="inlineStr"/>
-      <c r="Q61" s="1" t="inlineStr"/>
+      <c r="Q61" s="1" t="inlineStr">
+        <is>
+          <t>L1078: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: ♦ in order to ensure changes be-•</t>
+        </is>
+      </c>
       <c r="R61" s="1" t="inlineStr"/>
       <c r="S61" s="1" t="inlineStr"/>
       <c r="T61" s="1" t="inlineStr"/>
@@ -3804,21 +3636,17 @@
       <c r="H62" s="1" t="inlineStr"/>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1081: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: later than 9 a. m. on the day of â€¢</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L473: isolated marker/symbol line :: 107</t>
+          <t>L466: symbol-only separator/garbage line :: 140%</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>L758: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 39%</t>
+          <t>L721: symbol-only separator/garbage line :: .217%</t>
         </is>
       </c>
       <c r="P62" s="1" t="inlineStr"/>
@@ -3843,21 +3671,17 @@
       <c r="H63" s="1" t="inlineStr"/>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1083: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ publication.â€¢</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L475: isolated marker/symbol line :: .</t>
+          <t>L468: symbol-only separator/garbage line :: . 125%</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr">
         <is>
-          <t>L760: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...131%</t>
+          <t>L723: symbol-only separator/garbage line :: .55</t>
         </is>
       </c>
       <c r="P63" s="1" t="inlineStr"/>
@@ -3882,21 +3706,17 @@
       <c r="H64" s="1" t="inlineStr"/>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1085: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Hallâ€™s</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L477: symbol-only separator/garbage line :: 134% 4</t>
+          <t>L469: symbol-only separator/garbage line :: 126%</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr">
         <is>
-          <t>L762: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...29%</t>
+          <t>L756: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 31%</t>
         </is>
       </c>
       <c r="P64" s="1" t="inlineStr"/>
@@ -3921,21 +3741,17 @@
       <c r="H65" s="1" t="inlineStr"/>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L1091: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: â€˜Phone 244</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L479: symbol-only separator/garbage line :: 15114</t>
+          <t>L471: symbol-only separator/garbage line :: 35%</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>L768: symbol-only separator/garbage line :: .125%</t>
+          <t>L758: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 39%</t>
         </is>
       </c>
       <c r="P65" s="1" t="inlineStr"/>
@@ -3960,21 +3776,17 @@
       <c r="H66" s="1" t="inlineStr"/>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L1125: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: some interesting stereoptic viewâ€¢</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L483: symbol-only separator/garbage line :: 2314</t>
+          <t>L473: isolated marker/symbol line :: 107</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr">
         <is>
-          <t>L770: symbol-only separator/garbage line :: .35%</t>
+          <t>L760: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...131%</t>
         </is>
       </c>
       <c r="P66" s="1" t="inlineStr"/>
@@ -3999,21 +3811,17 @@
       <c r="H67" s="1" t="inlineStr"/>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L1160: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”DEALER INâ€”</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L485: isolated marker/symbol line :: 2</t>
+          <t>L475: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr">
         <is>
-          <t>L772: symbol-only separator/garbage line :: .106%</t>
+          <t>L762: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...29%</t>
         </is>
       </c>
       <c r="P67" s="1" t="inlineStr"/>
@@ -4043,12 +3851,12 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L486: symbol-only separator/garbage line :: 32%</t>
+          <t>L477: symbol-only separator/garbage line :: 134% 4</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>L774: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...15% - - |</t>
+          <t>L768: symbol-only separator/garbage line :: .125%</t>
         </is>
       </c>
       <c r="P68" s="1" t="inlineStr"/>
@@ -4078,12 +3886,12 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L488: isolated marker/symbol line :: 49</t>
+          <t>L479: symbol-only separator/garbage line :: 15114</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr">
         <is>
-          <t>L776: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...134% 134%</t>
+          <t>L770: symbol-only separator/garbage line :: .35%</t>
         </is>
       </c>
       <c r="P69" s="1" t="inlineStr"/>
@@ -4113,12 +3921,12 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L490: isolated marker/symbol line :: 110</t>
+          <t>L481: symbol-only separator/garbage line :: 27 ½</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr">
         <is>
-          <t>L778: symbol-only separator/garbage line | punctuation artifact: repeated periods :: , ..150% 151%</t>
+          <t>L772: symbol-only separator/garbage line :: .106%</t>
         </is>
       </c>
       <c r="P70" s="1" t="inlineStr"/>
@@ -4148,12 +3956,12 @@
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L492: symbol-only separator/garbage line :: 105%</t>
+          <t>L483: symbol-only separator/garbage line :: 2314</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>L780: symbol-only separator/garbage line :: . 26%</t>
+          <t>L774: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...15% - - |</t>
         </is>
       </c>
       <c r="P71" s="1" t="inlineStr"/>
@@ -4183,12 +3991,12 @@
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L493: isolated marker/symbol line :: ,</t>
+          <t>L485: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr">
         <is>
-          <t>L804: symbol-only separator/garbage line :: 27%</t>
+          <t>L776: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...134% 134%</t>
         </is>
       </c>
       <c r="P72" s="1" t="inlineStr"/>
@@ -4218,12 +4026,12 @@
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L504: isolated marker/symbol line :: 1</t>
+          <t>L486: symbol-only separator/garbage line :: 32%</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr">
         <is>
-          <t>L805: symbol-only separator/garbage line :: 23%</t>
+          <t>L778: symbol-only separator/garbage line | punctuation artifact: repeated periods :: , ..150% 151%</t>
         </is>
       </c>
       <c r="P73" s="1" t="inlineStr"/>
@@ -4253,12 +4061,12 @@
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L522: isolated marker/symbol line :: *</t>
+          <t>L488: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>L807: symbol-only separator/garbage line :: 32%</t>
+          <t>L780: symbol-only separator/garbage line :: . 26%</t>
         </is>
       </c>
       <c r="P74" s="1" t="inlineStr"/>
@@ -4288,12 +4096,12 @@
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L523: isolated marker/symbol line :: *</t>
+          <t>L490: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr">
         <is>
-          <t>L808: isolated marker/symbol line :: 49</t>
+          <t>L804: symbol-only separator/garbage line :: 27%</t>
         </is>
       </c>
       <c r="P75" s="1" t="inlineStr"/>
@@ -4323,12 +4131,12 @@
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L537: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L492: symbol-only separator/garbage line :: 105%</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr">
         <is>
-          <t>L809: isolated marker/symbol line :: 110</t>
+          <t>L805: symbol-only separator/garbage line :: 23%</t>
         </is>
       </c>
       <c r="P76" s="1" t="inlineStr"/>
@@ -4358,12 +4166,12 @@
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L568: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L493: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>L811: symbol-only separator/garbage line :: 105%</t>
+          <t>L807: symbol-only separator/garbage line :: 32%</t>
         </is>
       </c>
       <c r="P77" s="1" t="inlineStr"/>
@@ -4393,12 +4201,12 @@
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â€�</t>
+          <t>L504: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>L859: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..113% 112%</t>
+          <t>L808: isolated marker/symbol line :: 49</t>
         </is>
       </c>
       <c r="P78" s="1" t="inlineStr"/>
@@ -4428,12 +4236,12 @@
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L590: isolated marker/symbol line :: .</t>
+          <t>L522: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>L861: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..114% 114%</t>
+          <t>L809: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="P79" s="1" t="inlineStr"/>
@@ -4463,12 +4271,12 @@
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L591: isolated marker/symbol line :: 0</t>
+          <t>L523: isolated marker/symbol line :: *</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr">
         <is>
-          <t>L863: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..159% 159%</t>
+          <t>L811: symbol-only separator/garbage line :: 105%</t>
         </is>
       </c>
       <c r="P80" s="1" t="inlineStr"/>
@@ -4498,12 +4306,12 @@
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L600: isolated marker/symbol line :: A</t>
+          <t>L537: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr">
         <is>
-          <t>L867: symbol-only separator/garbage line :: 16%</t>
+          <t>L859: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..113% 112%</t>
         </is>
       </c>
       <c r="P81" s="1" t="inlineStr"/>
@@ -4533,12 +4341,12 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L615: isolated marker/symbol line :: I</t>
+          <t>L568: isolated marker/symbol line :: ”</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr">
         <is>
-          <t>L915: isolated marker/symbol line :: 17</t>
+          <t>L861: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..114% 114%</t>
         </is>
       </c>
       <c r="P82" s="1" t="inlineStr"/>
@@ -4568,12 +4376,12 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L625: isolated marker/symbol line :: y</t>
+          <t>L569: isolated marker/symbol line :: ”</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr">
         <is>
-          <t>L917: symbol-only separator/garbage line :: 91%</t>
+          <t>L863: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ..159% 159%</t>
         </is>
       </c>
       <c r="P83" s="1" t="inlineStr"/>
@@ -4603,12 +4411,12 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L626: isolated marker/symbol line :: 2</t>
+          <t>L590: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr">
         <is>
-          <t>L919: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ......126% 127%</t>
+          <t>L867: symbol-only separator/garbage line :: 16%</t>
         </is>
       </c>
       <c r="P84" s="1" t="inlineStr"/>
@@ -4638,12 +4446,12 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L627: isolated marker/symbol line :: S</t>
+          <t>L591: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr">
         <is>
-          <t>L921: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 24% 24%</t>
+          <t>L915: isolated marker/symbol line :: 17</t>
         </is>
       </c>
       <c r="P85" s="1" t="inlineStr"/>
@@ -4673,12 +4481,12 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L642: isolated marker/symbol line :: '</t>
+          <t>L600: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr">
         <is>
-          <t>L923: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 49% 49%</t>
+          <t>L917: symbol-only separator/garbage line :: 91%</t>
         </is>
       </c>
       <c r="P86" s="1" t="inlineStr"/>
@@ -4708,12 +4516,12 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L663: isolated marker/symbol line :: 4</t>
+          <t>L615: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr">
         <is>
-          <t>L925: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...149% 150%</t>
+          <t>L919: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ......126% 127%</t>
         </is>
       </c>
       <c r="P87" s="1" t="inlineStr"/>
@@ -4743,12 +4551,12 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L704: isolated marker/symbol line :: 0</t>
+          <t>L625: isolated marker/symbol line :: y</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr">
         <is>
-          <t>L927: symbol-only separator/garbage line :: 60 60%</t>
+          <t>L921: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 24% 24%</t>
         </is>
       </c>
       <c r="P88" s="1" t="inlineStr"/>
@@ -4778,12 +4586,12 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L705: stray/suspicious non-ASCII glyph(s): U+00A8 DIAERESIS | isolated marker/symbol line :: ç”¨</t>
+          <t>L626: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr">
         <is>
-          <t>L929: symbol-only separator/garbage line :: 60 60%</t>
+          <t>L923: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ... 49% 49%</t>
         </is>
       </c>
       <c r="P89" s="1" t="inlineStr"/>
@@ -4813,12 +4621,12 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L706: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L627: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr">
         <is>
-          <t>L931: symbol-only separator/garbage line :: 107%</t>
+          <t>L925: symbol-only separator/garbage line | punctuation artifact: repeated periods :: ...149% 150%</t>
         </is>
       </c>
       <c r="P90" s="1" t="inlineStr"/>
@@ -4848,12 +4656,12 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L707: stray/suspicious non-ASCII glyph(s): U+00B4 ACUTE ACCENT, U+00B8 CEDILLA | isolated marker/symbol line :: è´¸</t>
+          <t>L642: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr">
         <is>
-          <t>L933: isolated marker/symbol line :: 26</t>
+          <t>L927: symbol-only separator/garbage line :: 60 60%</t>
         </is>
       </c>
       <c r="P91" s="1" t="inlineStr"/>
@@ -4883,12 +4691,12 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L708: isolated marker/symbol line :: 2</t>
+          <t>L663: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr">
         <is>
-          <t>L935: symbol-only separator/garbage line :: 65%</t>
+          <t>L929: symbol-only separator/garbage line :: 60 60%</t>
         </is>
       </c>
       <c r="P92" s="1" t="inlineStr"/>
@@ -4918,12 +4726,12 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L719: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L704: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr">
         <is>
-          <t>L937: symbol-only separator/garbage line :: 92%</t>
+          <t>L931: symbol-only separator/garbage line :: 107%</t>
         </is>
       </c>
       <c r="P93" s="1" t="inlineStr"/>
@@ -4953,12 +4761,12 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L741: symbol-only separator/garbage line :: . 100</t>
+          <t>L705: stray/suspicious non-ASCII glyph(s): U+7528 CJK UNIFIED IDEOGRAPH-7528 | isolated marker/symbol line :: 用</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr">
         <is>
-          <t>L1012: symbol-only separator/garbage line | line starts with punctuation glued to text :: * 600</t>
+          <t>L933: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="P94" s="1" t="inlineStr"/>
@@ -4988,12 +4796,12 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L744: isolated marker/symbol line :: .</t>
+          <t>L706: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr">
         <is>
-          <t>L1037: isolated marker/symbol line :: N</t>
+          <t>L935: symbol-only separator/garbage line :: 65%</t>
         </is>
       </c>
       <c r="P95" s="1" t="inlineStr"/>
@@ -5023,12 +4831,12 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L746: symbol-only separator/garbage line :: . 113%</t>
+          <t>L707: stray/suspicious non-ASCII glyph(s): U+8D38 CJK UNIFIED IDEOGRAPH-8D38 | isolated marker/symbol line :: 贸</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr">
         <is>
-          <t>L1063: symbol-only separator/garbage line :: 100.</t>
+          <t>L937: symbol-only separator/garbage line :: 92%</t>
         </is>
       </c>
       <c r="P96" s="1" t="inlineStr"/>
@@ -5058,12 +4866,12 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L747: symbol-only separator/garbage line :: 112%</t>
+          <t>L708: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr">
         <is>
-          <t>L1070: symbol-only separator/garbage line :: 188.</t>
+          <t>L1012: symbol-only separator/garbage line | line starts with punctuation glued to text :: * 600</t>
         </is>
       </c>
       <c r="P97" s="1" t="inlineStr"/>
@@ -5093,12 +4901,12 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L749: symbol-only separator/garbage line :: 1141</t>
+          <t>L719: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr">
         <is>
-          <t>L1075: symbol-only separator/garbage line :: 8.4</t>
+          <t>L1037: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="P98" s="1" t="inlineStr"/>
@@ -5128,12 +4936,12 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L751: isolated marker/symbol line | punctuation artifact: double/multiple hyphen :: --</t>
+          <t>L741: symbol-only separator/garbage line :: . 100</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr">
         <is>
-          <t>L1087: isolated marker/symbol line :: e</t>
+          <t>L1063: symbol-only separator/garbage line :: 100.</t>
         </is>
       </c>
       <c r="P99" s="1" t="inlineStr"/>
@@ -5163,12 +4971,12 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L752: symbol-only separator/garbage line :: . 159%</t>
+          <t>L743: symbol-only separator/garbage line | punctuation artifact: repeated periods :: …... 20%</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr">
         <is>
-          <t>L1127: isolated marker/symbol line :: e</t>
+          <t>L1070: symbol-only separator/garbage line :: 188.</t>
         </is>
       </c>
       <c r="P100" s="1" t="inlineStr"/>
@@ -5198,12 +5006,12 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L753: symbol-only separator/garbage line :: 159%</t>
+          <t>L744: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr">
         <is>
-          <t>L1192: isolated marker/symbol line :: -</t>
+          <t>L1075: symbol-only separator/garbage line :: 8.4</t>
         </is>
       </c>
       <c r="P101" s="1" t="inlineStr"/>
@@ -5233,12 +5041,12 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L755: symbol-only separator/garbage line :: 23%</t>
+          <t>L746: symbol-only separator/garbage line :: . 113%</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr">
         <is>
-          <t>L1205: isolated marker/symbol line :: 0</t>
+          <t>L1087: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="P102" s="1" t="inlineStr"/>
@@ -5268,12 +5076,12 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L757: symbol-only separator/garbage line :: 16%</t>
+          <t>L747: symbol-only separator/garbage line :: 112%</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr">
         <is>
-          <t>L1211: isolated marker/symbol line :: U</t>
+          <t>L1127: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="P103" s="1" t="inlineStr"/>
@@ -5303,10 +5111,14 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L759: symbol-only separator/garbage line :: . 91%</t>
-        </is>
-      </c>
-      <c r="O104" s="1" t="inlineStr"/>
+          <t>L749: symbol-only separator/garbage line :: 1141</t>
+        </is>
+      </c>
+      <c r="O104" s="1" t="inlineStr">
+        <is>
+          <t>L1192: isolated marker/symbol line :: -</t>
+        </is>
+      </c>
       <c r="P104" s="1" t="inlineStr"/>
       <c r="Q104" s="1" t="inlineStr"/>
       <c r="R104" s="1" t="inlineStr"/>
@@ -5334,10 +5146,14 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L762: symbol-only separator/garbage line :: 127%</t>
-        </is>
-      </c>
-      <c r="O105" s="1" t="inlineStr"/>
+          <t>L751: isolated marker/symbol line | punctuation artifact: double/multiple hyphen :: --</t>
+        </is>
+      </c>
+      <c r="O105" s="1" t="inlineStr">
+        <is>
+          <t>L1205: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
       <c r="P105" s="1" t="inlineStr"/>
       <c r="Q105" s="1" t="inlineStr"/>
       <c r="R105" s="1" t="inlineStr"/>
@@ -5365,10 +5181,14 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L764: symbol-only separator/garbage line :: 24%</t>
-        </is>
-      </c>
-      <c r="O106" s="1" t="inlineStr"/>
+          <t>L752: symbol-only separator/garbage line :: . 159%</t>
+        </is>
+      </c>
+      <c r="O106" s="1" t="inlineStr">
+        <is>
+          <t>L1211: isolated marker/symbol line :: U</t>
+        </is>
+      </c>
       <c r="P106" s="1" t="inlineStr"/>
       <c r="Q106" s="1" t="inlineStr"/>
       <c r="R106" s="1" t="inlineStr"/>
@@ -5396,7 +5216,7 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L766: symbol-only separator/garbage line :: 49%</t>
+          <t>L753: symbol-only separator/garbage line :: 159%</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -5427,7 +5247,7 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L769: isolated marker/symbol line :: 150</t>
+          <t>L755: symbol-only separator/garbage line :: 23%</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -5458,7 +5278,7 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L771: symbol-only separator/garbage line :: 60%</t>
+          <t>L757: symbol-only separator/garbage line :: 16%</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -5489,7 +5309,7 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L773: symbol-only separator/garbage line :: 60%</t>
+          <t>L759: symbol-only separator/garbage line :: . 91%</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -5520,7 +5340,7 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L775: isolated marker/symbol line :: 107</t>
+          <t>L760: symbol-only separator/garbage line :: 92 ½</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -5551,7 +5371,7 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L777: isolated marker/symbol line :: 26</t>
+          <t>L762: symbol-only separator/garbage line :: 127%</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -5582,7 +5402,7 @@
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L779: symbol-only separator/garbage line :: 6514</t>
+          <t>L764: symbol-only separator/garbage line :: 24%</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr"/>
@@ -5613,7 +5433,7 @@
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L802: symbol-only separator/garbage line :: 100.</t>
+          <t>L766: symbol-only separator/garbage line :: 49%</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr"/>
@@ -5644,7 +5464,7 @@
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L807: symbol-only separator/garbage line :: 188.</t>
+          <t>L768: symbol-only separator/garbage line :: . 149 ½</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr"/>
@@ -5675,7 +5495,7 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L837: isolated marker/symbol line :: 2</t>
+          <t>L769: isolated marker/symbol line :: 150</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr"/>
@@ -5706,7 +5526,7 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L843: isolated marker/symbol line :: '</t>
+          <t>L771: symbol-only separator/garbage line :: 60%</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr"/>
@@ -5737,7 +5557,7 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L844: isolated marker/symbol line :: 7</t>
+          <t>L773: symbol-only separator/garbage line :: 60%</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr"/>
@@ -5768,7 +5588,7 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L850: symbol-only separator/garbage line :: $15, 000, 000</t>
+          <t>L775: isolated marker/symbol line :: 107</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr"/>
@@ -5799,7 +5619,7 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L858: symbol-only separator/garbage line :: 8.4</t>
+          <t>L777: isolated marker/symbol line :: 26</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr"/>
@@ -5830,7 +5650,7 @@
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L860: isolated marker/symbol line :: '</t>
+          <t>L779: symbol-only separator/garbage line :: 6514</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr"/>
@@ -5861,7 +5681,7 @@
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L861: isolated marker/symbol line :: +</t>
+          <t>L802: symbol-only separator/garbage line :: 100.</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr"/>
@@ -5892,7 +5712,7 @@
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L866: isolated marker/symbol line :: E</t>
+          <t>L807: symbol-only separator/garbage line :: 188.</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr"/>
@@ -5923,7 +5743,7 @@
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L871: isolated marker/symbol line :: F</t>
+          <t>L837: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr"/>
@@ -5954,7 +5774,7 @@
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L875: isolated marker/symbol line :: .</t>
+          <t>L843: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr"/>
@@ -5985,7 +5805,7 @@
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L883: isolated marker/symbol line :: 600</t>
+          <t>L844: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr"/>
@@ -6016,7 +5836,7 @@
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L884: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L850: symbol-only separator/garbage line :: $15, 000, 000</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr"/>
@@ -6047,7 +5867,7 @@
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L896: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L858: symbol-only separator/garbage line :: 8.4</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr"/>
@@ -6078,7 +5898,7 @@
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L898: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L860: isolated marker/symbol line :: '</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr"/>
@@ -6093,6 +5913,285 @@
       <c r="X129" s="1" t="inlineStr"/>
       <c r="Y129" s="1" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr"/>
+      <c r="B130" s="1" t="inlineStr"/>
+      <c r="C130" s="1" t="inlineStr"/>
+      <c r="D130" s="1" t="inlineStr"/>
+      <c r="E130" s="1" t="inlineStr"/>
+      <c r="F130" s="1" t="inlineStr"/>
+      <c r="G130" s="1" t="inlineStr"/>
+      <c r="H130" s="1" t="inlineStr"/>
+      <c r="I130" s="1" t="inlineStr"/>
+      <c r="J130" s="1" t="inlineStr"/>
+      <c r="K130" s="1" t="inlineStr"/>
+      <c r="L130" s="1" t="inlineStr"/>
+      <c r="M130" s="1" t="inlineStr"/>
+      <c r="N130" s="1" t="inlineStr">
+        <is>
+          <t>L861: isolated marker/symbol line :: +</t>
+        </is>
+      </c>
+      <c r="O130" s="1" t="inlineStr"/>
+      <c r="P130" s="1" t="inlineStr"/>
+      <c r="Q130" s="1" t="inlineStr"/>
+      <c r="R130" s="1" t="inlineStr"/>
+      <c r="S130" s="1" t="inlineStr"/>
+      <c r="T130" s="1" t="inlineStr"/>
+      <c r="U130" s="1" t="inlineStr"/>
+      <c r="V130" s="1" t="inlineStr"/>
+      <c r="W130" s="1" t="inlineStr"/>
+      <c r="X130" s="1" t="inlineStr"/>
+      <c r="Y130" s="1" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr"/>
+      <c r="B131" s="1" t="inlineStr"/>
+      <c r="C131" s="1" t="inlineStr"/>
+      <c r="D131" s="1" t="inlineStr"/>
+      <c r="E131" s="1" t="inlineStr"/>
+      <c r="F131" s="1" t="inlineStr"/>
+      <c r="G131" s="1" t="inlineStr"/>
+      <c r="H131" s="1" t="inlineStr"/>
+      <c r="I131" s="1" t="inlineStr"/>
+      <c r="J131" s="1" t="inlineStr"/>
+      <c r="K131" s="1" t="inlineStr"/>
+      <c r="L131" s="1" t="inlineStr"/>
+      <c r="M131" s="1" t="inlineStr"/>
+      <c r="N131" s="1" t="inlineStr">
+        <is>
+          <t>L866: isolated marker/symbol line :: E</t>
+        </is>
+      </c>
+      <c r="O131" s="1" t="inlineStr"/>
+      <c r="P131" s="1" t="inlineStr"/>
+      <c r="Q131" s="1" t="inlineStr"/>
+      <c r="R131" s="1" t="inlineStr"/>
+      <c r="S131" s="1" t="inlineStr"/>
+      <c r="T131" s="1" t="inlineStr"/>
+      <c r="U131" s="1" t="inlineStr"/>
+      <c r="V131" s="1" t="inlineStr"/>
+      <c r="W131" s="1" t="inlineStr"/>
+      <c r="X131" s="1" t="inlineStr"/>
+      <c r="Y131" s="1" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr"/>
+      <c r="B132" s="1" t="inlineStr"/>
+      <c r="C132" s="1" t="inlineStr"/>
+      <c r="D132" s="1" t="inlineStr"/>
+      <c r="E132" s="1" t="inlineStr"/>
+      <c r="F132" s="1" t="inlineStr"/>
+      <c r="G132" s="1" t="inlineStr"/>
+      <c r="H132" s="1" t="inlineStr"/>
+      <c r="I132" s="1" t="inlineStr"/>
+      <c r="J132" s="1" t="inlineStr"/>
+      <c r="K132" s="1" t="inlineStr"/>
+      <c r="L132" s="1" t="inlineStr"/>
+      <c r="M132" s="1" t="inlineStr"/>
+      <c r="N132" s="1" t="inlineStr">
+        <is>
+          <t>L871: isolated marker/symbol line :: F</t>
+        </is>
+      </c>
+      <c r="O132" s="1" t="inlineStr"/>
+      <c r="P132" s="1" t="inlineStr"/>
+      <c r="Q132" s="1" t="inlineStr"/>
+      <c r="R132" s="1" t="inlineStr"/>
+      <c r="S132" s="1" t="inlineStr"/>
+      <c r="T132" s="1" t="inlineStr"/>
+      <c r="U132" s="1" t="inlineStr"/>
+      <c r="V132" s="1" t="inlineStr"/>
+      <c r="W132" s="1" t="inlineStr"/>
+      <c r="X132" s="1" t="inlineStr"/>
+      <c r="Y132" s="1" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr"/>
+      <c r="B133" s="1" t="inlineStr"/>
+      <c r="C133" s="1" t="inlineStr"/>
+      <c r="D133" s="1" t="inlineStr"/>
+      <c r="E133" s="1" t="inlineStr"/>
+      <c r="F133" s="1" t="inlineStr"/>
+      <c r="G133" s="1" t="inlineStr"/>
+      <c r="H133" s="1" t="inlineStr"/>
+      <c r="I133" s="1" t="inlineStr"/>
+      <c r="J133" s="1" t="inlineStr"/>
+      <c r="K133" s="1" t="inlineStr"/>
+      <c r="L133" s="1" t="inlineStr"/>
+      <c r="M133" s="1" t="inlineStr"/>
+      <c r="N133" s="1" t="inlineStr">
+        <is>
+          <t>L875: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O133" s="1" t="inlineStr"/>
+      <c r="P133" s="1" t="inlineStr"/>
+      <c r="Q133" s="1" t="inlineStr"/>
+      <c r="R133" s="1" t="inlineStr"/>
+      <c r="S133" s="1" t="inlineStr"/>
+      <c r="T133" s="1" t="inlineStr"/>
+      <c r="U133" s="1" t="inlineStr"/>
+      <c r="V133" s="1" t="inlineStr"/>
+      <c r="W133" s="1" t="inlineStr"/>
+      <c r="X133" s="1" t="inlineStr"/>
+      <c r="Y133" s="1" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr"/>
+      <c r="B134" s="1" t="inlineStr"/>
+      <c r="C134" s="1" t="inlineStr"/>
+      <c r="D134" s="1" t="inlineStr"/>
+      <c r="E134" s="1" t="inlineStr"/>
+      <c r="F134" s="1" t="inlineStr"/>
+      <c r="G134" s="1" t="inlineStr"/>
+      <c r="H134" s="1" t="inlineStr"/>
+      <c r="I134" s="1" t="inlineStr"/>
+      <c r="J134" s="1" t="inlineStr"/>
+      <c r="K134" s="1" t="inlineStr"/>
+      <c r="L134" s="1" t="inlineStr"/>
+      <c r="M134" s="1" t="inlineStr"/>
+      <c r="N134" s="1" t="inlineStr">
+        <is>
+          <t>L883: isolated marker/symbol line :: 600</t>
+        </is>
+      </c>
+      <c r="O134" s="1" t="inlineStr"/>
+      <c r="P134" s="1" t="inlineStr"/>
+      <c r="Q134" s="1" t="inlineStr"/>
+      <c r="R134" s="1" t="inlineStr"/>
+      <c r="S134" s="1" t="inlineStr"/>
+      <c r="T134" s="1" t="inlineStr"/>
+      <c r="U134" s="1" t="inlineStr"/>
+      <c r="V134" s="1" t="inlineStr"/>
+      <c r="W134" s="1" t="inlineStr"/>
+      <c r="X134" s="1" t="inlineStr"/>
+      <c r="Y134" s="1" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr"/>
+      <c r="B135" s="1" t="inlineStr"/>
+      <c r="C135" s="1" t="inlineStr"/>
+      <c r="D135" s="1" t="inlineStr"/>
+      <c r="E135" s="1" t="inlineStr"/>
+      <c r="F135" s="1" t="inlineStr"/>
+      <c r="G135" s="1" t="inlineStr"/>
+      <c r="H135" s="1" t="inlineStr"/>
+      <c r="I135" s="1" t="inlineStr"/>
+      <c r="J135" s="1" t="inlineStr"/>
+      <c r="K135" s="1" t="inlineStr"/>
+      <c r="L135" s="1" t="inlineStr"/>
+      <c r="M135" s="1" t="inlineStr"/>
+      <c r="N135" s="1" t="inlineStr">
+        <is>
+          <t>L884: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="O135" s="1" t="inlineStr"/>
+      <c r="P135" s="1" t="inlineStr"/>
+      <c r="Q135" s="1" t="inlineStr"/>
+      <c r="R135" s="1" t="inlineStr"/>
+      <c r="S135" s="1" t="inlineStr"/>
+      <c r="T135" s="1" t="inlineStr"/>
+      <c r="U135" s="1" t="inlineStr"/>
+      <c r="V135" s="1" t="inlineStr"/>
+      <c r="W135" s="1" t="inlineStr"/>
+      <c r="X135" s="1" t="inlineStr"/>
+      <c r="Y135" s="1" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr"/>
+      <c r="B136" s="1" t="inlineStr"/>
+      <c r="C136" s="1" t="inlineStr"/>
+      <c r="D136" s="1" t="inlineStr"/>
+      <c r="E136" s="1" t="inlineStr"/>
+      <c r="F136" s="1" t="inlineStr"/>
+      <c r="G136" s="1" t="inlineStr"/>
+      <c r="H136" s="1" t="inlineStr"/>
+      <c r="I136" s="1" t="inlineStr"/>
+      <c r="J136" s="1" t="inlineStr"/>
+      <c r="K136" s="1" t="inlineStr"/>
+      <c r="L136" s="1" t="inlineStr"/>
+      <c r="M136" s="1" t="inlineStr"/>
+      <c r="N136" s="1" t="inlineStr">
+        <is>
+          <t>L896: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="O136" s="1" t="inlineStr"/>
+      <c r="P136" s="1" t="inlineStr"/>
+      <c r="Q136" s="1" t="inlineStr"/>
+      <c r="R136" s="1" t="inlineStr"/>
+      <c r="S136" s="1" t="inlineStr"/>
+      <c r="T136" s="1" t="inlineStr"/>
+      <c r="U136" s="1" t="inlineStr"/>
+      <c r="V136" s="1" t="inlineStr"/>
+      <c r="W136" s="1" t="inlineStr"/>
+      <c r="X136" s="1" t="inlineStr"/>
+      <c r="Y136" s="1" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr"/>
+      <c r="B137" s="1" t="inlineStr"/>
+      <c r="C137" s="1" t="inlineStr"/>
+      <c r="D137" s="1" t="inlineStr"/>
+      <c r="E137" s="1" t="inlineStr"/>
+      <c r="F137" s="1" t="inlineStr"/>
+      <c r="G137" s="1" t="inlineStr"/>
+      <c r="H137" s="1" t="inlineStr"/>
+      <c r="I137" s="1" t="inlineStr"/>
+      <c r="J137" s="1" t="inlineStr"/>
+      <c r="K137" s="1" t="inlineStr"/>
+      <c r="L137" s="1" t="inlineStr"/>
+      <c r="M137" s="1" t="inlineStr"/>
+      <c r="N137" s="1" t="inlineStr">
+        <is>
+          <t>L898: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="O137" s="1" t="inlineStr"/>
+      <c r="P137" s="1" t="inlineStr"/>
+      <c r="Q137" s="1" t="inlineStr"/>
+      <c r="R137" s="1" t="inlineStr"/>
+      <c r="S137" s="1" t="inlineStr"/>
+      <c r="T137" s="1" t="inlineStr"/>
+      <c r="U137" s="1" t="inlineStr"/>
+      <c r="V137" s="1" t="inlineStr"/>
+      <c r="W137" s="1" t="inlineStr"/>
+      <c r="X137" s="1" t="inlineStr"/>
+      <c r="Y137" s="1" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr"/>
+      <c r="B138" s="1" t="inlineStr"/>
+      <c r="C138" s="1" t="inlineStr"/>
+      <c r="D138" s="1" t="inlineStr"/>
+      <c r="E138" s="1" t="inlineStr"/>
+      <c r="F138" s="1" t="inlineStr"/>
+      <c r="G138" s="1" t="inlineStr"/>
+      <c r="H138" s="1" t="inlineStr"/>
+      <c r="I138" s="1" t="inlineStr"/>
+      <c r="J138" s="1" t="inlineStr"/>
+      <c r="K138" s="1" t="inlineStr"/>
+      <c r="L138" s="1" t="inlineStr"/>
+      <c r="M138" s="1" t="inlineStr"/>
+      <c r="N138" s="1" t="inlineStr">
+        <is>
+          <t>L943: stray/suspicious non-ASCII glyph(s): U+6E90 CJK UNIFIED IDEOGRAPH-6E90 | isolated marker/symbol line :: 源</t>
+        </is>
+      </c>
+      <c r="O138" s="1" t="inlineStr"/>
+      <c r="P138" s="1" t="inlineStr"/>
+      <c r="Q138" s="1" t="inlineStr"/>
+      <c r="R138" s="1" t="inlineStr"/>
+      <c r="S138" s="1" t="inlineStr"/>
+      <c r="T138" s="1" t="inlineStr"/>
+      <c r="U138" s="1" t="inlineStr"/>
+      <c r="V138" s="1" t="inlineStr"/>
+      <c r="W138" s="1" t="inlineStr"/>
+      <c r="X138" s="1" t="inlineStr"/>
+      <c r="Y138" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
